--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_OBRADOIRO AMES.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_OBRADOIRO AMES.xlsx
@@ -565,13 +565,13 @@
         <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>22.6355</v>
+        <v>17.4497</v>
       </c>
       <c r="E2" t="n">
-        <v>26.7972</v>
+        <v>21.5154</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.161700000000001</v>
+        <v>-4.065200000000001</v>
       </c>
       <c r="G2" t="n">
         <v>11.8851</v>
@@ -610,13 +610,13 @@
         <v>35.8398</v>
       </c>
       <c r="S2" t="n">
-        <v>15.8145</v>
+        <v>10.6292</v>
       </c>
       <c r="T2" t="n">
-        <v>10.0753</v>
+        <v>4.7931</v>
       </c>
       <c r="U2" t="n">
-        <v>5.7394</v>
+        <v>5.8359</v>
       </c>
       <c r="V2" t="n">
         <v>-1.7346</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ TAPIA</t>
+          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>7.888699999999999</v>
+        <v>16.8085</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.525700000000001</v>
+        <v>21.2362</v>
       </c>
       <c r="F3" t="n">
-        <v>10.4143</v>
+        <v>-4.427700000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.338100000000001</v>
+        <v>0.4719000000000007</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1231</v>
+        <v>-1.462199999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.2152</v>
+        <v>1.933899999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>5.83</v>
+        <v>30.8984</v>
       </c>
       <c r="K3" t="n">
-        <v>4.527699999999999</v>
+        <v>22.3935</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3023</v>
+        <v>8.505000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-8.1685</v>
+        <v>-30.4267</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.6505</v>
+        <v>-23.8553</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.5179</v>
+        <v>-6.571</v>
       </c>
       <c r="P3" t="n">
-        <v>5.2879</v>
+        <v>-0.5876000000000003</v>
       </c>
       <c r="Q3" t="n">
-        <v>-18.0178</v>
+        <v>-38.3859</v>
       </c>
       <c r="R3" t="n">
-        <v>23.3057</v>
+        <v>37.7985</v>
       </c>
       <c r="S3" t="n">
-        <v>10.2412</v>
+        <v>9.694800000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>5.2442</v>
+        <v>2.7077</v>
       </c>
       <c r="U3" t="n">
-        <v>4.997</v>
+        <v>6.9871</v>
       </c>
       <c r="V3" t="n">
-        <v>-5.302</v>
+        <v>7.2296</v>
       </c>
       <c r="W3" t="n">
-        <v>4.418299999999999</v>
+        <v>26.017</v>
       </c>
       <c r="X3" t="n">
-        <v>-9.7203</v>
+        <v>-18.7875</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
+          <t>Á. SONEIRA BOO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>7.292999999999998</v>
+        <v>11.5533</v>
       </c>
       <c r="E4" t="n">
-        <v>16.3971</v>
+        <v>5.494400000000002</v>
       </c>
       <c r="F4" t="n">
-        <v>-9.104200000000001</v>
+        <v>6.058999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4719000000000007</v>
+        <v>16.4313</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.462199999999999</v>
+        <v>-4.946000000000002</v>
       </c>
       <c r="I4" t="n">
-        <v>1.933899999999999</v>
+        <v>21.3774</v>
       </c>
       <c r="J4" t="n">
-        <v>30.8984</v>
+        <v>38.169</v>
       </c>
       <c r="K4" t="n">
-        <v>22.3935</v>
+        <v>11.9735</v>
       </c>
       <c r="L4" t="n">
-        <v>8.505000000000001</v>
+        <v>26.195</v>
       </c>
       <c r="M4" t="n">
-        <v>-30.4267</v>
+        <v>-21.7376</v>
       </c>
       <c r="N4" t="n">
-        <v>-23.8553</v>
+        <v>-16.9197</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.571</v>
+        <v>-4.8179</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5876000000000003</v>
+        <v>-13.3176</v>
       </c>
       <c r="Q4" t="n">
-        <v>-38.3859</v>
+        <v>-50.5288</v>
       </c>
       <c r="R4" t="n">
-        <v>37.7985</v>
+        <v>37.211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1789999999999998</v>
+        <v>0.3140000000000002</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.1315</v>
+        <v>-1.9185</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3106</v>
+        <v>2.2328</v>
       </c>
       <c r="V4" t="n">
-        <v>7.2296</v>
+        <v>8.1258</v>
       </c>
       <c r="W4" t="n">
-        <v>26.017</v>
+        <v>19.7738</v>
       </c>
       <c r="X4" t="n">
-        <v>-18.7875</v>
+        <v>-11.6479</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Á. SONEIRA BOO</t>
+          <t>S. RODRÍGUEZ TAPIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>3.434800000000001</v>
+        <v>5.803200000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01489999999999725</v>
+        <v>-3.6713</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4195</v>
+        <v>9.474499999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>16.4313</v>
+        <v>-2.338100000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.946000000000002</v>
+        <v>-1.1231</v>
       </c>
       <c r="I5" t="n">
-        <v>21.3774</v>
+        <v>-1.2152</v>
       </c>
       <c r="J5" t="n">
-        <v>38.169</v>
+        <v>5.83</v>
       </c>
       <c r="K5" t="n">
-        <v>11.9735</v>
+        <v>4.527699999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>26.195</v>
+        <v>1.3023</v>
       </c>
       <c r="M5" t="n">
-        <v>-21.7376</v>
+        <v>-8.1685</v>
       </c>
       <c r="N5" t="n">
-        <v>-16.9197</v>
+        <v>-5.6505</v>
       </c>
       <c r="O5" t="n">
-        <v>-4.8179</v>
+        <v>-2.5179</v>
       </c>
       <c r="P5" t="n">
-        <v>-13.3176</v>
+        <v>5.2879</v>
       </c>
       <c r="Q5" t="n">
-        <v>-50.5288</v>
+        <v>-18.0178</v>
       </c>
       <c r="R5" t="n">
-        <v>37.211</v>
+        <v>23.3057</v>
       </c>
       <c r="S5" t="n">
-        <v>-7.805000000000001</v>
+        <v>8.1556</v>
       </c>
       <c r="T5" t="n">
-        <v>-7.3981</v>
+        <v>4.0985</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4064000000000003</v>
+        <v>4.0569</v>
       </c>
       <c r="V5" t="n">
-        <v>8.1258</v>
+        <v>-5.302</v>
       </c>
       <c r="W5" t="n">
-        <v>19.7738</v>
+        <v>4.418299999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-11.6479</v>
+        <v>-9.7203</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. SOLNTSEV REMIRO</t>
+          <t>N. FUENTES PRADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1083</v>
+        <v>3.0643</v>
       </c>
       <c r="E6" t="n">
-        <v>1.842</v>
+        <v>-0.7853999999999992</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2663</v>
+        <v>3.849800000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3517</v>
+        <v>-0.7468999999999997</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1752</v>
+        <v>-5.996</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1765</v>
+        <v>5.249</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1203</v>
+        <v>8.129</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2012</v>
+        <v>0.02839999999999995</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0808</v>
+        <v>8.1004</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7685999999999999</v>
+        <v>-8.8759</v>
       </c>
       <c r="N6" t="n">
-        <v>1.026</v>
+        <v>-6.025</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2573</v>
+        <v>-2.8516</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5668</v>
+        <v>-5.0921</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-17.6261</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5668</v>
+        <v>12.534</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8931</v>
+        <v>-0.2213</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4703</v>
+        <v>-0.9057999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4228</v>
+        <v>0.6847000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>9.124599999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>1.492</v>
+        <v>9.617799999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.492</v>
+        <v>-0.4931999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. BAZAL GARCIA</t>
+          <t>I. SOLNTSEV REMIRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0818</v>
+        <v>1.7954</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4953</v>
+        <v>0.7163</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5771</v>
+        <v>1.0792</v>
       </c>
       <c r="G7" t="n">
-        <v>4.006</v>
+        <v>-0.3517</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9089</v>
+        <v>-0.1752</v>
       </c>
       <c r="I7" t="n">
-        <v>3.0971</v>
+        <v>-0.1765</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1873</v>
+        <v>-1.1203</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4287</v>
+        <v>-1.2012</v>
       </c>
       <c r="L7" t="n">
-        <v>3.7586</v>
+        <v>0.0808</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1813</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4802</v>
+        <v>1.026</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6615</v>
+        <v>-0.2573</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1958</v>
+        <v>1.5668</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5750999999999999</v>
+        <v>0.5803</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7128</v>
+        <v>0.3446</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1377</v>
+        <v>0.2357</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.3169</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.3169</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. CANEDA FONTOIRA</t>
+          <t>P. BAZAL GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9364</v>
+        <v>0.4255</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.699</v>
+        <v>3.0828</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2375</v>
+        <v>-2.6573</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6375</v>
+        <v>4.006</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.375</v>
+        <v>0.9089</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2625</v>
+        <v>3.0971</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5802</v>
+        <v>4.1873</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5802</v>
+        <v>0.4287</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.7586</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0573</v>
+        <v>-0.1813</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2052</v>
+        <v>0.4802</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2625</v>
+        <v>-0.6615</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5875</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5875</v>
+        <v>0.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6111</v>
+        <v>-0.0678</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1188</v>
+        <v>-0.1253</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4923</v>
+        <v>0.0575</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2754</v>
+        <v>-3.3169</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2754</v>
+        <v>-3.3169</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SYLLA</t>
+          <t>M. CANEDA FONTOIRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3564</v>
+        <v>-0.8562</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.8593</v>
+        <v>-0.699</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5029</v>
+        <v>-0.1573</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9284</v>
+        <v>-0.6375</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8113000000000001</v>
+        <v>-0.375</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1171</v>
+        <v>-0.2625</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06079999999999997</v>
+        <v>-0.5802</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6263000000000001</v>
+        <v>-0.5802</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6869999999999999</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.8675</v>
+        <v>-0.0573</v>
       </c>
       <c r="N9" t="n">
-        <v>1.4373</v>
+        <v>0.2052</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4301</v>
+        <v>-0.2625</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7833000000000001</v>
+        <v>0.5875</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3708</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1543</v>
+        <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0265</v>
+        <v>-0.5309</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2186</v>
+        <v>-0.1188</v>
       </c>
       <c r="U9" t="n">
-        <v>0.192</v>
+        <v>-0.4121</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.0415</v>
+        <v>-0.2754</v>
       </c>
       <c r="W9" t="n">
-        <v>-2.3306</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7108999999999999</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. FUENTES PRADO</t>
+          <t>M. SYLLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7087</v>
+        <v>-1.1291</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5453</v>
+        <v>-4.9022</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8367</v>
+        <v>3.7731</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7468999999999997</v>
+        <v>1.9284</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.996</v>
+        <v>0.8113000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>5.249</v>
+        <v>1.1171</v>
       </c>
       <c r="J10" t="n">
-        <v>8.129</v>
+        <v>0.06079999999999997</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02839999999999995</v>
+        <v>-0.6263000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>8.1004</v>
+        <v>0.6869999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-8.8759</v>
+        <v>1.8675</v>
       </c>
       <c r="N10" t="n">
-        <v>-6.025</v>
+        <v>1.4373</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.8516</v>
+        <v>0.4301</v>
       </c>
       <c r="P10" t="n">
-        <v>-5.0921</v>
+        <v>0.7833000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-17.6261</v>
+        <v>-1.3708</v>
       </c>
       <c r="R10" t="n">
-        <v>12.534</v>
+        <v>2.1543</v>
       </c>
       <c r="S10" t="n">
-        <v>-5.994199999999999</v>
+        <v>-0.7994</v>
       </c>
       <c r="T10" t="n">
-        <v>-4.6657</v>
+        <v>-1.2615</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3286</v>
+        <v>0.4622</v>
       </c>
       <c r="V10" t="n">
-        <v>9.124599999999999</v>
+        <v>-3.0415</v>
       </c>
       <c r="W10" t="n">
-        <v>9.617799999999999</v>
+        <v>-2.3306</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.4931999999999999</v>
+        <v>-0.7108999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7784</v>
+        <v>-1.5605</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4083</v>
+        <v>-1.4873</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3702</v>
+        <v>-0.07340000000000002</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5709</v>
@@ -1312,13 +1312,13 @@
         <v>2.1543</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9494</v>
+        <v>0.2685</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0516</v>
+        <v>-0.1306</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1022</v>
+        <v>0.3991</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4332</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B. FRAGA CANTELAR</t>
+          <t>Y. REY CONDE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9192</v>
+        <v>-2.679599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4357</v>
+        <v>-2.8221</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.355</v>
+        <v>0.1424000000000004</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7914</v>
+        <v>-1.0253</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7965</v>
+        <v>-2.8033</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.995</v>
+        <v>1.778</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1677999999999998</v>
+        <v>2.877799999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>1.3302</v>
+        <v>-0.5700999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1624</v>
+        <v>3.4481</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.9593</v>
+        <v>-3.9033</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.127</v>
+        <v>-2.2333</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1673999999999999</v>
+        <v>-1.67</v>
       </c>
       <c r="P12" t="n">
-        <v>1.175</v>
+        <v>0.5874000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.175</v>
+        <v>-6.0713</v>
       </c>
       <c r="R12" t="n">
-        <v>2.35</v>
+        <v>6.6587</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1890000000000001</v>
+        <v>-1.6334</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8345000000000001</v>
+        <v>-0.8451</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6456</v>
+        <v>-0.7882</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.492</v>
+        <v>-0.6083000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6083</v>
+        <v>1.2166</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1003</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. MARTINEZ CARRO</t>
+          <t>B. FRAGA CANTELAR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8386</v>
+        <v>-3.1829</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.6023</v>
+        <v>-0.1782000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7637</v>
+        <v>-3.0047</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.5963</v>
+        <v>-2.7914</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3043</v>
+        <v>-1.7965</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.9006</v>
+        <v>-0.995</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.1557</v>
+        <v>0.1677999999999998</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0938</v>
+        <v>1.3302</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.2495</v>
+        <v>-1.1624</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4407</v>
+        <v>-2.9593</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2103</v>
+        <v>-3.127</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6511</v>
+        <v>0.1673999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7833</v>
+        <v>1.175</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9584</v>
+        <v>-1.175</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7417</v>
+        <v>2.35</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5337000000000001</v>
+        <v>-0.07459999999999997</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4882000000000001</v>
+        <v>0.2205</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.04559999999999997</v>
+        <v>-0.2951</v>
       </c>
       <c r="V13" t="n">
         <v>-1.492</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.6083</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.492</v>
+        <v>-2.1003</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H. MATEO MERELLES</t>
+          <t>T. MARTINEZ CARRO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.9292</v>
+        <v>-4.0746</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.3567</v>
+        <v>-4.7046</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5726</v>
+        <v>0.6299000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.3952</v>
+        <v>-2.5963</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.5042</v>
+        <v>1.3043</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.891</v>
+        <v>-3.9006</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.5048</v>
+        <v>-2.1557</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5987</v>
+        <v>1.0938</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.1035</v>
+        <v>-3.2495</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.890499999999999</v>
+        <v>-0.4407</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.103</v>
+        <v>0.2103</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.7875</v>
+        <v>-0.6511</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5874</v>
+        <v>0.7833</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9376</v>
+        <v>-1.9584</v>
       </c>
       <c r="R14" t="n">
-        <v>3.5251</v>
+        <v>2.7417</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7621</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4187</v>
+        <v>-0.5905</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3433</v>
+        <v>-0.1792</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8836999999999999</v>
+        <v>-1.492</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5508</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Y. REY CONDE</t>
+          <t>H. MATEO MERELLES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.0703</v>
+        <v>-4.7849</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.3307</v>
+        <v>-4.3997</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7396</v>
+        <v>-0.3855</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.0253</v>
+        <v>-6.3952</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.8033</v>
+        <v>-1.5042</v>
       </c>
       <c r="I15" t="n">
-        <v>1.778</v>
+        <v>-4.891</v>
       </c>
       <c r="J15" t="n">
-        <v>2.877799999999999</v>
+        <v>-1.5048</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5700999999999999</v>
+        <v>0.5987</v>
       </c>
       <c r="L15" t="n">
-        <v>3.4481</v>
+        <v>-2.1035</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.9033</v>
+        <v>-4.890499999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.2333</v>
+        <v>-2.103</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.67</v>
+        <v>-2.7875</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5874000000000001</v>
+        <v>0.5874</v>
       </c>
       <c r="Q15" t="n">
-        <v>-6.0713</v>
+        <v>-2.9376</v>
       </c>
       <c r="R15" t="n">
-        <v>6.6587</v>
+        <v>3.5251</v>
       </c>
       <c r="S15" t="n">
-        <v>-4.0241</v>
+        <v>1.9063</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.3537</v>
+        <v>0.3757999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.6705</v>
+        <v>1.5306</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6083000000000001</v>
+        <v>-0.8836999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2166</v>
+        <v>-0.3329</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8249</v>
+        <v>-0.5508</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.9092</v>
+        <v>-6.4531</v>
       </c>
       <c r="E16" t="n">
-        <v>-10.0069</v>
+        <v>-7.656699999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>4.0975</v>
+        <v>1.2035</v>
       </c>
       <c r="G16" t="n">
         <v>-18.0032</v>
@@ -1702,13 +1702,13 @@
         <v>28.7895</v>
       </c>
       <c r="S16" t="n">
-        <v>8.2608</v>
+        <v>7.716699999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.7744</v>
+        <v>0.5755999999999998</v>
       </c>
       <c r="U16" t="n">
-        <v>10.0352</v>
+        <v>7.1411</v>
       </c>
       <c r="V16" t="n">
         <v>3.6375</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. RODRÍGUEZ BLANCO</t>
+          <t>M. QITTANE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>-12.7594</v>
+        <v>-12.0526</v>
       </c>
       <c r="E17" t="n">
-        <v>-10.0028</v>
+        <v>-0.5430000000000006</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.7571</v>
+        <v>-11.5097</v>
       </c>
       <c r="G17" t="n">
-        <v>-10.1115</v>
+        <v>-8.994399999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-6.3895</v>
+        <v>-1.5337</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.7221</v>
+        <v>-7.4609</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.3449</v>
+        <v>2.3324</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4243000000000004</v>
+        <v>4.2336</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9207</v>
+        <v>-1.9013</v>
       </c>
       <c r="M17" t="n">
-        <v>-7.7666</v>
+        <v>-11.3268</v>
       </c>
       <c r="N17" t="n">
-        <v>-5.9653</v>
+        <v>-5.7674</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.8015</v>
+        <v>-5.5596</v>
       </c>
       <c r="P17" t="n">
-        <v>-4.3088</v>
+        <v>-4.1128</v>
       </c>
       <c r="Q17" t="n">
-        <v>-13.3177</v>
+        <v>-10.7715</v>
       </c>
       <c r="R17" t="n">
-        <v>9.008699999999999</v>
+        <v>6.6587</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8207</v>
+        <v>-1.3787</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3432</v>
+        <v>-0.1140000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5224</v>
+        <v>-1.2646</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1601999999999999</v>
+        <v>2.4333</v>
       </c>
       <c r="W17" t="n">
-        <v>3.3169</v>
+        <v>8.0106</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.4771</v>
+        <v>-5.577299999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. QITTANE</t>
+          <t>M. RODRÍGUEZ BLANCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>-13.5885</v>
+        <v>-12.1892</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3782</v>
+        <v>-10.7024</v>
       </c>
       <c r="F18" t="n">
-        <v>-12.2102</v>
+        <v>-1.4866</v>
       </c>
       <c r="G18" t="n">
-        <v>-8.994399999999999</v>
+        <v>-10.1115</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5337</v>
+        <v>-6.3895</v>
       </c>
       <c r="I18" t="n">
-        <v>-7.4609</v>
+        <v>-3.7221</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3324</v>
+        <v>-2.3449</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2336</v>
+        <v>-0.4243000000000004</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9013</v>
+        <v>-1.9207</v>
       </c>
       <c r="M18" t="n">
-        <v>-11.3268</v>
+        <v>-7.7666</v>
       </c>
       <c r="N18" t="n">
-        <v>-5.7674</v>
+        <v>-5.9653</v>
       </c>
       <c r="O18" t="n">
-        <v>-5.5596</v>
+        <v>-1.8015</v>
       </c>
       <c r="P18" t="n">
-        <v>-4.1128</v>
+        <v>-4.3088</v>
       </c>
       <c r="Q18" t="n">
-        <v>-10.7715</v>
+        <v>-13.3177</v>
       </c>
       <c r="R18" t="n">
-        <v>6.6587</v>
+        <v>9.008699999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.9143</v>
+        <v>2.3909</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9492</v>
+        <v>1.6432</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.965</v>
+        <v>0.7477999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>2.4333</v>
+        <v>-0.1601999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>8.0106</v>
+        <v>3.3169</v>
       </c>
       <c r="X18" t="n">
-        <v>-5.577299999999999</v>
+        <v>-3.4771</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y. PINAS</t>
+          <t>R. DÍAZ DEL VALLE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>-13.7838</v>
+        <v>-15.832</v>
       </c>
       <c r="E19" t="n">
-        <v>-14.1281</v>
+        <v>-14.8176</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3441000000000006</v>
+        <v>-1.0143</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.990599999999999</v>
+        <v>-0.7350000000000012</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7139</v>
+        <v>-2.253099999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.7042</v>
+        <v>1.518099999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>13.9626</v>
+        <v>18.5386</v>
       </c>
       <c r="K19" t="n">
-        <v>11.3307</v>
+        <v>11.9052</v>
       </c>
       <c r="L19" t="n">
-        <v>2.6315</v>
+        <v>6.6334</v>
       </c>
       <c r="M19" t="n">
-        <v>-15.9532</v>
+        <v>-19.2736</v>
       </c>
       <c r="N19" t="n">
-        <v>-10.6171</v>
+        <v>-14.1584</v>
       </c>
       <c r="O19" t="n">
-        <v>-5.3362</v>
+        <v>-5.1152</v>
       </c>
       <c r="P19" t="n">
-        <v>-12.5343</v>
+        <v>-15.472</v>
       </c>
       <c r="Q19" t="n">
-        <v>-40.5404</v>
+        <v>-39.7573</v>
       </c>
       <c r="R19" t="n">
-        <v>28.0061</v>
+        <v>24.2852</v>
       </c>
       <c r="S19" t="n">
-        <v>15.3278</v>
+        <v>5.5997</v>
       </c>
       <c r="T19" t="n">
-        <v>7.827</v>
+        <v>-0.3100000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>7.5011</v>
+        <v>5.9097</v>
       </c>
       <c r="V19" t="n">
-        <v>-14.5868</v>
+        <v>-5.2244</v>
       </c>
       <c r="W19" t="n">
-        <v>4.623699999999999</v>
+        <v>6.7113</v>
       </c>
       <c r="X19" t="n">
-        <v>-19.2105</v>
+        <v>-11.9359</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>Y. PINAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>-17.6914</v>
+        <v>-19.8212</v>
       </c>
       <c r="E20" t="n">
-        <v>-16.4641</v>
+        <v>-18.9413</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.227299999999999</v>
+        <v>-0.8795999999999997</v>
       </c>
       <c r="G20" t="n">
-        <v>-23.4119</v>
+        <v>-1.990599999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-11.6392</v>
+        <v>0.7139</v>
       </c>
       <c r="I20" t="n">
-        <v>-11.773</v>
+        <v>-2.7042</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5592</v>
+        <v>13.9626</v>
       </c>
       <c r="K20" t="n">
-        <v>5.014900000000001</v>
+        <v>11.3307</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.4557</v>
+        <v>2.6315</v>
       </c>
       <c r="M20" t="n">
-        <v>-26.9712</v>
+        <v>-15.9532</v>
       </c>
       <c r="N20" t="n">
-        <v>-16.6538</v>
+        <v>-10.6171</v>
       </c>
       <c r="O20" t="n">
-        <v>-10.3173</v>
+        <v>-5.3362</v>
       </c>
       <c r="P20" t="n">
-        <v>-6.071300000000001</v>
+        <v>-12.5343</v>
       </c>
       <c r="Q20" t="n">
         <v>-40.5404</v>
       </c>
       <c r="R20" t="n">
-        <v>34.469</v>
+        <v>28.0061</v>
       </c>
       <c r="S20" t="n">
-        <v>13.8473</v>
+        <v>9.2905</v>
       </c>
       <c r="T20" t="n">
-        <v>9.3177</v>
+        <v>3.0134</v>
       </c>
       <c r="U20" t="n">
-        <v>4.5297</v>
+        <v>6.2772</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.055</v>
+        <v>-14.5868</v>
       </c>
       <c r="W20" t="n">
-        <v>11.1998</v>
+        <v>4.623699999999999</v>
       </c>
       <c r="X20" t="n">
-        <v>-13.2551</v>
+        <v>-19.2105</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Q. HUANG</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>-19.416</v>
+        <v>-21.9255</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.488399999999999</v>
+        <v>-21.4126</v>
       </c>
       <c r="F21" t="n">
-        <v>-10.9276</v>
+        <v>-0.5124999999999995</v>
       </c>
       <c r="G21" t="n">
-        <v>11.6068</v>
+        <v>-23.4119</v>
       </c>
       <c r="H21" t="n">
-        <v>3.8987</v>
+        <v>-11.6392</v>
       </c>
       <c r="I21" t="n">
-        <v>7.7082</v>
+        <v>-11.773</v>
       </c>
       <c r="J21" t="n">
-        <v>30.6067</v>
+        <v>3.5592</v>
       </c>
       <c r="K21" t="n">
-        <v>18.6071</v>
+        <v>5.014900000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>11.9996</v>
+        <v>-1.4557</v>
       </c>
       <c r="M21" t="n">
-        <v>-18.9995</v>
+        <v>-26.9712</v>
       </c>
       <c r="N21" t="n">
-        <v>-14.7081</v>
+        <v>-16.6538</v>
       </c>
       <c r="O21" t="n">
-        <v>-4.2914</v>
+        <v>-10.3173</v>
       </c>
       <c r="P21" t="n">
-        <v>-30.9442</v>
+        <v>-6.071300000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>-54.6416</v>
+        <v>-40.5404</v>
       </c>
       <c r="R21" t="n">
-        <v>23.6975</v>
+        <v>34.469</v>
       </c>
       <c r="S21" t="n">
-        <v>4.903</v>
+        <v>9.613099999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>5.0134</v>
+        <v>4.3691</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1102999999999998</v>
+        <v>5.2441</v>
       </c>
       <c r="V21" t="n">
-        <v>-4.9815</v>
+        <v>-2.055</v>
       </c>
       <c r="W21" t="n">
-        <v>10.5337</v>
+        <v>11.1998</v>
       </c>
       <c r="X21" t="n">
-        <v>-15.5155</v>
+        <v>-13.2551</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. DÍAZ DEL VALLE</t>
+          <t>Q. HUANG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,70 +2122,70 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D22" t="n">
-        <v>-20.6571</v>
+        <v>-22.7285</v>
       </c>
       <c r="E22" t="n">
-        <v>-20.0862</v>
+        <v>-11.7402</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5710999999999999</v>
+        <v>-10.9881</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7350000000000012</v>
+        <v>11.6068</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.253099999999999</v>
+        <v>3.8987</v>
       </c>
       <c r="I22" t="n">
-        <v>1.518099999999999</v>
+        <v>7.7082</v>
       </c>
       <c r="J22" t="n">
-        <v>18.5386</v>
+        <v>30.6067</v>
       </c>
       <c r="K22" t="n">
-        <v>11.9052</v>
+        <v>18.6071</v>
       </c>
       <c r="L22" t="n">
-        <v>6.6334</v>
+        <v>11.9996</v>
       </c>
       <c r="M22" t="n">
-        <v>-19.2736</v>
+        <v>-18.9995</v>
       </c>
       <c r="N22" t="n">
-        <v>-14.1584</v>
+        <v>-14.7081</v>
       </c>
       <c r="O22" t="n">
-        <v>-5.1152</v>
+        <v>-4.2914</v>
       </c>
       <c r="P22" t="n">
-        <v>-15.472</v>
+        <v>-30.9442</v>
       </c>
       <c r="Q22" t="n">
-        <v>-39.7573</v>
+        <v>-54.6416</v>
       </c>
       <c r="R22" t="n">
-        <v>24.2852</v>
+        <v>23.6975</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7744000000000002</v>
+        <v>1.5906</v>
       </c>
       <c r="T22" t="n">
-        <v>-5.5785</v>
+        <v>1.7615</v>
       </c>
       <c r="U22" t="n">
-        <v>6.3532</v>
+        <v>-0.1706</v>
       </c>
       <c r="V22" t="n">
-        <v>-5.2244</v>
+        <v>-4.9815</v>
       </c>
       <c r="W22" t="n">
-        <v>6.7113</v>
+        <v>10.5337</v>
       </c>
       <c r="X22" t="n">
-        <v>-11.9359</v>
+        <v>-15.5155</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>25</v>
       </c>
       <c r="D23" t="n">
-        <v>-31.6788</v>
+        <v>-24.9881</v>
       </c>
       <c r="E23" t="n">
-        <v>-23.7256</v>
+        <v>-19.7811</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.953200000000001</v>
+        <v>-5.206799999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-20.6729</v>
@@ -2248,13 +2248,13 @@
         <v>26.4392</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.4058</v>
+        <v>-0.7150000000000003</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.946099999999999</v>
+        <v>-1.0014</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.4592</v>
+        <v>0.2867</v>
       </c>
       <c r="V23" t="n">
         <v>-7.5173</v>
@@ -2281,13 +2281,13 @@
         <v>25</v>
       </c>
       <c r="D24" t="n">
-        <v>-115.7429</v>
+        <v>-97.35809999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-84.62540000000001</v>
+        <v>-77.19959999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-31.11940000000001</v>
+        <v>-20.1573</v>
       </c>
       <c r="G24" t="n">
         <v>-55.0433</v>
@@ -2296,7 +2296,7 @@
         <v>-39.8456</v>
       </c>
       <c r="I24" t="n">
-        <v>-15.1986</v>
+        <v>-15.19860000000001</v>
       </c>
       <c r="J24" t="n">
         <v>196.0849</v>
@@ -2305,7 +2305,7 @@
         <v>137.204</v>
       </c>
       <c r="L24" t="n">
-        <v>58.87979999999999</v>
+        <v>58.8798</v>
       </c>
       <c r="M24" t="n">
         <v>-251.1287</v>
@@ -2320,19 +2320,19 @@
         <v>-79.3194</v>
       </c>
       <c r="Q24" t="n">
-        <v>-429.8845999999999</v>
+        <v>-429.8846</v>
       </c>
       <c r="R24" t="n">
         <v>350.5647</v>
       </c>
       <c r="S24" t="n">
-        <v>43.1737</v>
+        <v>61.5594</v>
       </c>
       <c r="T24" t="n">
-        <v>9.1571</v>
+        <v>16.5815</v>
       </c>
       <c r="U24" t="n">
-        <v>34.0183</v>
+        <v>44.97930000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-24.554</v>
